--- a/donation_forms/021_hospital_cancer_research_donation_form--donation_forms.xlsx
+++ b/donation_forms/021_hospital_cancer_research_donation_form--donation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -777,12 +777,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>donor_notes</t>
+          <t>donor_notes_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Donor notes</t>
+          <t>Donor Notes 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -915,12 +915,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>payment_details</t>
+          <t>payment_details_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>payment details</t>
+          <t>Payment Details 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>donor_status</t>
+          <t>donor_status_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Donor status</t>
+          <t>Donor Status 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>donor_status</t>
+          <t>donor_status_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Donor status</t>
+          <t>Donor Status 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>donor_status</t>
+          <t>donor_status_4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>donor status</t>
+          <t>Donor Status 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>donor_status</t>
+          <t>donor_status_5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>donor status</t>
+          <t>Donor Status 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
